--- a/ADR_MPC_Project_Timeline.xlsx
+++ b/ADR_MPC_Project_Timeline.xlsx
@@ -1,19 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leonardo\Desktop\6 DOF-Project\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAFA79E-AB04-4EEC-B39B-697884ED6B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Project Timeline" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Learning Plan" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Target Labs" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Project Timeline" sheetId="1" r:id="rId1"/>
+    <sheet name="Learning Plan" sheetId="2" r:id="rId2"/>
+    <sheet name="Target Labs" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -24,784 +40,782 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="256">
   <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duration (days)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel / Sequencing Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deliverable / Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 0 – Setup &amp; Literature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learn Git &amp; GitHub basics (init, add, commit, push, .gitignore, README, basic branching); create the GitHub repository (L1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do this before writing a single line of project code — see chat for the concrete repo structure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learn Python fundamentals coming from MATLAB: syntax, NumPy arrays &amp; 0-based indexing, functions, control flow (L2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Tasks 1, 3, 4, 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No prior Python experience assumed — budget real time for this.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set up Python environment (venv), VS Code + Jupyter integration, requirements.txt; build folder structure inside the repo (dynamics/, mpc/, sim/, tests/, docs/, notebooks/); first commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After Task 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read 3–4 recent LA3 (Colin Jones) papers + skim rendezvous/ADR MPC literature (survey-level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Tasks 1, 2, 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is what makes the motivation letter specific instead of generic.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study linear systems &amp; state-space representation (L3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Tasks 1–4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study CW derivation, assumptions, forced response &amp; ZOH discretization theory (L4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 4, after Task 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 1 – Translational Dynamics (3-DoF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derive continuous-time CW state-space model (A, B) in LVLH frame, including the control-acceleration input; write-up per L19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Math write-up before any code.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discretize (ZOH / state transition matrix), implement propagator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit tests: propagator vs. analytic CW solution (free-drift ellipse check)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First real test in tests/ — not optional.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study state estimation / noise modeling basics (L5), then add Gaussian process + measurement noise to the sim, with a basic Kalman filter feeding the controller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 9 tail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Without this, the whole project assumes perfect knowledge — a real weak point. If time is tight, the minimal KF can slip to just before Task 20.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build nonlinear two-body plant (sim/) + CW-vs-nonlinear sweep over target eccentricity e and separation ρ (L20); short write-up: CW linearization assumptions &amp; validity limits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 10 and start of Task 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goes in docs/ — one page is enough. Sweep above SL-16's e≈1e-3 is a stress test, label it as such. End date moved 9→11 Oct; Phase 2 opens with study tasks, so no critical-path impact.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 2 – Linear MPC (Translational)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study convex optimization fundamentals (L6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 13 start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study MPC theory: receding horizon, cost design, terminal ingredients, stability intro (L7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formulate QP/SOCP: cost function, horizon N, thrust constraints, keep-out / approach-cone constraints (hard) — convex modeling per L21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write the formulation doc before opening CVXPY.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study soft constraints &amp; recursive feasibility basics (L8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extend formulation with soft constraints (slack variables) for guaranteed feasibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talking point #1 for the interview.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study CVXPY practical usage (L9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implement linear MPC in CVXPY (nominal, noiseless case)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed-loop nominal simulation + core metrics (fuel/Δv consumption, settling time, constraint violations)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First real deliverable — usable in CV/interview from here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed-loop Monte Carlo simulation under navigation noise + CW-vs-plant mismatch (dispersion plots, robustness check; L22)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talking point #2: how the controller degrades under realistic uncertainty.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit tests for MPC module (feasibility checks, solver status handling)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document Phase 1–2 results (plots, metrics table) in repo README/report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is what you screen-share if interviewed early.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application (parallel track)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align motivation letter language with LA3 + shortlisted labs' recent papers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Phase 0–1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draft CV bullets + motivation letter using Phase 1–2 results/plots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Phase 2 tail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MILESTONE: Submit E3 application (up to 3 lab choices, CV, transcripts, statement of purpose, ID)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hard deadline — confirmed on eee.epfl.ch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal opens Oct 2026, closes Nov 1, 2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep GitHub repo continuously updated &amp; interview-ready (rolling — do not batch this at the end)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Runs in parallel with everything below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interviews can happen any time Nov–early Mar — the repo must be presentable throughout, not just in January.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 3 – Rotational Dynamics (3-DoF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study attitude kinematics &amp; dynamics: quaternions/MRPs, Euler's equations (L10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formulate nonlinear attitude dynamics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linearize (small-angle / MRP) for use inside a linear MPC (L11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 28 tail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit tests: attitude propagator validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4 – Rotational MPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study RW/RCS actuator constraints &amp; torque allocation basics (L12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formulate attitude MPC (torque/momentum saturation, soft constraints where needed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implement + closed-loop detumble/pointing simulation + metrics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monte Carlo robustness test under attitude estimation noise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTFOLIO CHECKPOINT #1: integrate translational + rotational results into one unified report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safe fallback deliverable if the interview happens before Phase 5 is mature.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 5 – Nonlinear Coupled 6-DoF MPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study NMPC theory: multiple shooting, direct collocation, SQP/interior-point basics (L13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study CasADi practical usage + example patterns (L14)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 36 tail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study solver internals: why OSQP/ECOS for QP vs. IPOPT for NLP, warm-starting (L15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 37 / holidays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formulate coupled nonlinear 6-DoF model (translation–rotation coupling via docking-port offset; L23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is the 'frontier' you present as in-progress at the interview.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implement NMPC in CasADi (multiple shooting), first working closed-loop test case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A rough working version is enough — do not over-polish before validating it works at all.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full validation suite: Monte Carlo over initial conditions + noise, metrics table, solver-time stats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recursive feasibility / terminal set discussion — analytical or qualitative write-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Task 41 tail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Even a qualitative discussion is a strong interview talking point.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTFOLIO CHECKPOINT #2: full 6-DoF results integrated into repo + report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No hard deadline — extend if needed, this is research-grade work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is fine — expected, even — for this to still be open at interview time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 6 – Stretch Goals (optional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study robust / tube MPC concepts (L17) — directly ties to LA3's own research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explore a robust or tube-based MPC extension on the translational subsystem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional — only if Phase 5 finished with time to spare.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional: simple synthetic vision-based relative pose estimation module (closes the GNC sense loop; L24)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can run parallel with Task 45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relevant if targeting Cavallaro/LIDIAP as a lab choice — see Target Labs sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional: learning-based MPC exploration (e.g. Gaussian process or NN model-mismatch correction; L25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ties back to your original AI/ML interest without abandoning the control core.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepare a short conference-style write-up/poster of the full project as a standalone portfolio artifact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good to have before the internship itself starts (May–Oct 2027).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interview Prep (parallel track)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepare talking points: CW → linear MPC → 6-DoF NMPC narrative, open problems, stability/feasibility discussion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel with Phase 3 start — do this early, interviews can start mid-Nov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mock technical interview (self Q&amp;A or with a peer/professor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repeat again in Jan/Feb if the interview hasn't happened yet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab-specific Q&amp;A prep: re-read papers of whichever lab actually invites you, anticipate questions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling — triggered by an actual interview invite, not a fixed date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See Target Labs sheet for the shortlist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Results</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MILESTONE: E3 results communicated by EPFL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm exact date on eee.epfl.ch — currently 'around mid-March 2027' per official FAQ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legend:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shaded rows = milestones/deadlines (fixed dates, not flexible tasks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progress summary:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks in progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks not started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needed For (Project Task)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study By Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git &amp; GitHub fundamentals: init, add, commit, push, .gitignore, README, basic branching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 1 (repo setup) — before writing any project code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GitHub's official 'Hello World' guide (docs.github.com); Git Handbook / Pro Git book ch. 1–2 (free, git-scm.com/book)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python fundamentals for MATLAB users: syntax, NumPy arrays &amp; 0-based indexing, functions, control flow, list/dict basics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 3 (environment setup) and everything after — first time using Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NumPy official 'NumPy for MATLAB users' guide (numpy.org); Python official tutorial ch. 3–4 (docs.python.org)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linear systems &amp; state-space representation (A, B matrices, controllability), matrix exponential, forced response (variation-of-constants formula)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 7 (CW state-space formulation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Åström &amp; Murray, 'Feedback Systems': ch. 5 (linear systems: matrix exponential, convolution/forced response) and §6.1 (reachability); ch. 2–4 as background only. Verify numbering against your edition. Second source: Wie §2.5 (Modern State-Space Methods) and §1.3. Or your intro control course notes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clohessy-Wiltshire equations: derivation, assumptions, forced response with control acceleration, ZOH discretization (A_d, B_d), impulsive vs. continuous thrust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks 7–8 (CW model + discretization); Task 6 (study)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curtis ch. 7 §7.4 (CW equations, state transition matrix Φ — homogeneous solution only, no control input); Wie §4.6 (Orbital Rendezvous) for CW. Wie §2.4 (ZOH) is Laplace-domain only — skip it. ZOH / sampling with input: Åström &amp; Wittenmark 'Computer-Controlled Systems' (sampling of continuous-time systems) or, preferred, Franklin, Powell &amp; Workman 'Digital Control of Dynamic Systems': §4.3.3 (state-space form of the ZOH discretization, Φ and Γ) and §4.3.5 (numerical computation of Φ and Γ). Their Φ, Γ = your A_d, B_d. Skip the z-transform sections. Practice: expm of augmented matrix [[A,B],[0,0]]·dt, check vs. closed-form Φ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State estimation &amp; noise modeling basics: process/measurement noise, discrete Kalman filter (implement the LTI case so the MPC acts on an estimated state)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 10 (adding realistic navigation uncertainty)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simon, 'Optimal State Estimation', ch. 1–5 (or any intro Kalman filter tutorial, e.g. Welch &amp; Bishop's classic KF tutorial, UNC). Practice: write a 6-state KF on the CW model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Convex optimization fundamentals: convex sets/functions, QP structure, why convexity matters for solvers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 14 (QP formulation for linear MPC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boyd &amp; Vandenberghe, 'Convex Optimization', ch. 1–4 (free PDF); Stanford EE364a lecture videos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPC theory: receding horizon principle, cost function design, prediction matrices (condensed vs. sparse formulation), LQR / DARE for the terminal cost, terminal set, stability intro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks 14, 18–19 (Linear MPC formulation + implementation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rawlings, Mayne &amp; Diehl, 'Model Predictive Control: Theory, Computation, and Design' (free PDF), ch. 1–2 (ch. 1 has the LQR/prediction-matrix material). Practice: scipy.linalg.solve_discrete_are for P; compare unconstrained MPC with LQR as a sanity check.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soft constraints &amp; recursive feasibility in MPC (slack variables, exact penalty functions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 16 (soft-constrained MPC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rawlings/Mayne/Diehl ch. 2 (constraint handling) + ch. 3 intro; Kerrigan &amp; Maciejowski, 'Soft constraints and exact penalty functions in MPC' (paper, freely searchable). Study-by moved from 23 Oct to 21 Oct: Task 16 starts 21 Oct.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CVXPY practical usage: problem setup, parameters vs. variables, solving MPC in a loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 18 (Linear MPC implementation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cvxpy.org official tutorial + examples gallery (MPC example specifically)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attitude kinematics &amp; dynamics: quaternions or MRPs, Euler's rotational equations of motion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 27–28 (rotational dynamics formulation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schaub &amp; Junkins, 'Analytical Mechanics of Space Systems', ch. 3–4; Wie ch. 5 (§5.4 quaternions, §5.5 kinematic differential equations) and ch. 6 (§6.4 Euler's rotational equations, §6.10 rigid body in a circular orbit).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linearization techniques for attitude models (small-angle, MRP linearization) for use inside a linear MPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 29 (linearized attitude state-space model)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schaub &amp; Junkins ch. 4; Wie ch. 5 (kinematics, for the linearization) and §7.3 (quaternion-feedback reorientation, as classical baseline vs. the MPC).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reaction wheel / RCS actuator constraints: torque/momentum saturation, allocation basics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 31–32 (rotational MPC with actuator constraints)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wie, 'Space Vehicle Dynamics and Control': §7.4 (attitude control and momentum management: wheel torque/momentum saturation), §7.6 (optimal jet selection logic, for RCS allocation). §7.5 (CMG) not needed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nonlinear programming for control: direct multiple shooting, collocation, SQP/interior-point basics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks 36, 39 (NMPC formulation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diehl &amp; Gros, 'Numerical Optimal Control' (free PDF, syscop.de); Rawlings/Mayne/Diehl ch. 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CasADi practical usage: symbolic modeling, nlpsol, multiple-shooting implementation pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 40 (NMPC implementation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">casadi.org 'Getting started' + official example pack (rocket/robot MPC examples)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solver internals: QP solvers (OSQP, ECOS) vs. NLP solvers (IPOPT), warm-starting, why the choice matters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks 38, 40 — and a common interview question</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSQP paper (Stellato et al., free); IPOPT documentation intro; CasADi docs section on solver plugins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPC stability &amp; recursive feasibility in depth (Lyapunov-based terminal ingredients) + invariant sets / terminal set computation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 42 + Task 49 (interview talking points)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rawlings/Mayne/Diehl, ch. 2–3 (stability chapters) — read a first pass early (by mid-Nov) since interviews can start then; revisit before Task 42. Invariant sets: Blanchini &amp; Miani, 'Set-Theoretic Methods in Control' (recognize the vocabulary); MPT3 toolbox docs (mpt3.org) for intuition on invariant-set computation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robust / tube MPC — conceptual overview (Prof. Jones' group works on this; recognize the vocabulary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 44 + interview talking points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rawlings/Mayne/Diehl ch. 3 (robust MPC section); skim 2–3 recent LA3 (Colin Jones) papers on epfl.ch/labs/la3. Study-by moved from 20 Nov to 15 Oct: the conceptual pass has to feed the motivation letter (Task 23, 1–15 Oct) and the 1 Nov submission. Refine in Phase 6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scientific Python toolkit &amp; testing: matplotlib for report-quality plots, SciPy (linalg.expm, integrate.solve_ivp), pytest + numpy.testing.assert_allclose (tolerances), Jupyter workflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks 3, 8, 9, 21 (first code + first tests in tests/)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matplotlib official tutorials ('Quick start'); SciPy docs for scipy.linalg.expm and scipy.integrate.solve_ivp; pytest 'Get started' (docs.pytest.org); NumPy docs for numpy.testing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical documentation: LaTeX (or Markdown with math) for formulation docs, equation/figure conventions, README structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks 7, 11, 14, 22, 35 (math write-ups before code)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overleaf 'Learn LaTeX in 30 minutes' + amsmath basics; or GitHub docs on math in Markdown. Half a day is enough.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nonlinear relative dynamics &amp; numerical propagation: inertial two-body propagation, inertial→LVLH transform of the relative state, effect of target eccentricity, J2 / differential drag as optional plant perturbations (plant vs. controller-model mismatch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks 9, 11, 20 (nonlinear plant, CW-vs-nonlinear sweep, Monte Carlo mismatch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curtis ch. 7 §7.2 (nonlinear relative motion equations); Wie §3.6 (orbital perturbations) or Vallado, 'Fundamentals of Astrodynamics and Applications' — only for the optional terms; SciPy solve_ivp docs (rtol/atol choice).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Convex modeling of MPC constraints &amp; costs: second-order cone constraints, ‖u‖₂ ≤ u_max vs. box limits, L1/L2 fuel-cost norms vs. quadratic cost, approach cone / line-of-sight as SOC, convexifying the keep-out zone, slack penalties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks 14, 16 (constraint set of the QP/SOCP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boyd &amp; Vandenberghe ch. 4 (§4.4: QP and SOCP); CVXPY docs, 'Disciplined Convex Programming' page; rendezvous-MPC papers collected in Task 4 (e.g. Hartley et al., 'Model predictive control system design and implementation for spacecraft rendezvous', Control Eng. Practice, 2012 — verify).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monte Carlo methodology: sampling initial conditions &amp; noise, seeded reproducibility (numpy.random.Generator), dispersion/percentile metrics, number of runs vs. confidence, reporting constraint-violation rates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks 20, 34, 41 (robustness studies)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NumPy docs, 'Random Generator'; copy the dispersion-reporting conventions from the papers read in Task 4.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-DoF coupling kinematics: docking-port lever arm (r_dock = r_cm + R·b), velocity/acceleration of an offset point, torques from off-axis thrust, relative pose in LVLH, unit-quaternion norm handling in NMPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 39 (coupled 6-DoF model)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schaub &amp; Junkins ch. 3–4 (rigid-body kinematics, revisit); Wie ch. 5–6 (kinematics + rigid-body dynamics, §6.10 for the orbit coupling) and §7.4/§7.6 (actuators); Fehse, 'Automated Rendezvous and Docking of Spacecraft' (Cambridge, 2003); coupled 6-DoF MPC papers for proximity operations (collect in Task 37).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPTIONAL — Vision-based relative pose estimation: pinhole camera model, PnP / feature-based pose from a known 3D model, pose uncertainty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 46 (optional stretch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hartley &amp; Zisserman, 'Multiple View Geometry in Computer Vision', ch. 6 (camera models) — verify; OpenCV solvePnP tutorial (docs.opencv.org).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPTIONAL — Learning-based MPC: Gaussian-process regression, model-mismatch correction inside MPC, safety via constraint tightening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 47 (optional stretch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rasmussen &amp; Williams, 'Gaussian Processes for Machine Learning', ch. 2 (free PDF); Hewing et al., 'Learning-based model predictive control: toward safe learning in control', Annu. Rev. Control Robot. Auton. Syst., 2020 — verify.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topics done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topics in progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topics not started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Areas (from EPFL listing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why It Fits This Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fit Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colin Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatic Control Laboratory 3 (LA3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control Systems, Optimization, Robotics &amp; Autonomous Systems, Learning &amp; Decision Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPC is literally their core research output. Your CW→linear MPC→6-DoF NMPC roadmap is a direct, self-contained application case study of what this lab does daily.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRIMARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maryam Kamgarpour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Control and Multiagent Optimization Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning &amp; Decision Systems, Robotics and Autonomous Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimization-under-constraints is the exact spine of your QP/NMPC formulation work — strong second choice inside the same sub-field as Jones, not a dilution of your pitch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STRONG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alireza Karimi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data-Driven Modelling and Control Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data &amp; Network Sciences, Energy Systems, Learning &amp; Decision Systems, Robotics, Theory and Simulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System identification + robust control. Your noise-robustness testing (Monte Carlo under navigation uncertainty) speaks directly to what this group cares about.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Giancarlo Ferrari Trecate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dependable Control and Decision group (DECAR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning &amp; Decision Systems, Mechanical Engineering, Energy Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distributed/robust control theory overlaps with your feasibility and soft-constraint work. Note from earlier discussion: PI has an Italian academic background (Pavia/Polimi-adjacent), which may make your 110L and rigor easier to contextualize.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrea Cavallaro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIDIAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imaging &amp; Vision, Learning &amp; Decision Systems, Robotics and Autonomous Systems, Sports Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relevant only if you build the optional Phase 6 vision/pose-estimation stretch goal (Task 46) — that closes the 'Sense' half of the GNC loop for a non-cooperative target. Weaker fit if you stay purely on the control side.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MODERATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anja Skrivervik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCI STI AS Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical Engineering, Flexible Electronics, Personalized Health, Robotics and Autonomous Systems, Space Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explicit Space Technology tag — useful if you want to keep the ADR framing front-and-center rather than pivoting the pitch fully toward generic autonomous systems. Verify current project focus before listing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farhad Rachidi-Haeri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCI STI FR Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical Engineering, Energy Systems, Space Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Space Technology tag present, but the group's recent work may skew toward EM/energy rather than GNC — check the lab's current project list on epfl.ch before including as one of your 3 choices.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MODERATE (verify first)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note on the E3 application form:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The E3 form asks for up to 3 lab choices. Recommended combination given your project: 1) Colin Jones (LA3) — primary; 2) Kamgarpour or Karimi — same control/optimization core, not a dilution of the pitch; 3) Ferrari Trecate — still control theory, different flavor (distributed/robust). Keep all 3 inside control &amp; optimization rather than mixing in a vision or space-hardware lab, so the motivation letter tells one coherent story.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beyond E3 (separate processes, same project transfers directly):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETH Zürich Robotics Student Summer Fellowship — Robotic Systems Lab (Hutter) or Autonomous Systems Lab (Siegwart). Not part of E3; separate application process and deadline (check ethz.ch directly). Your 6-DoF MPC ADR project is an equally strong pitch there, since both labs value real-time optimization-based control on physical/simulated systems. If E3 doesn't work out, a direct email to a PhD student in either lab (proposing a Master Thesis) is also a standard, lower-barrier path in — worth keeping as a parallel option rather than waiting for E3 results in March.</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Duration (days)</t>
+  </si>
+  <si>
+    <t>Parallel / Sequencing Notes</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Deliverable / Notes</t>
+  </si>
+  <si>
+    <t>Phase 0 – Setup &amp; Literature</t>
+  </si>
+  <si>
+    <t>Learn Git &amp; GitHub basics (init, add, commit, push, .gitignore, README, basic branching); create the GitHub repository (L1)</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Do this before writing a single line of project code — see chat for the concrete repo structure.</t>
+  </si>
+  <si>
+    <t>Learn Python fundamentals coming from MATLAB: syntax, NumPy arrays &amp; 0-based indexing, functions, control flow (L2)</t>
+  </si>
+  <si>
+    <t>Parallel with Tasks 1, 3, 4, 5</t>
+  </si>
+  <si>
+    <t>In progress</t>
+  </si>
+  <si>
+    <t>No prior Python experience assumed — budget real time for this.</t>
+  </si>
+  <si>
+    <t>Set up Python environment (venv), VS Code + Jupyter integration, requirements.txt; build folder structure inside the repo (dynamics/, mpc/, sim/, tests/, docs/, notebooks/); first commit</t>
+  </si>
+  <si>
+    <t>After Task 1</t>
+  </si>
+  <si>
+    <t>Read 3–4 recent LA3 (Colin Jones) papers + skim rendezvous/ADR MPC literature (survey-level)</t>
+  </si>
+  <si>
+    <t>Parallel with Tasks 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Not started</t>
+  </si>
+  <si>
+    <t>This is what makes the motivation letter specific instead of generic.</t>
+  </si>
+  <si>
+    <t>Study linear systems &amp; state-space representation (L3)</t>
+  </si>
+  <si>
+    <t>Parallel with Tasks 1–4</t>
+  </si>
+  <si>
+    <t>Study CW derivation, assumptions, forced response &amp; ZOH discretization theory (L4)</t>
+  </si>
+  <si>
+    <t>Parallel with Task 4, after Task 5</t>
+  </si>
+  <si>
+    <t>Phase 1 – Translational Dynamics (3-DoF)</t>
+  </si>
+  <si>
+    <t>Derive continuous-time CW state-space model (A, B) in LVLH frame, including the control-acceleration input; write-up per L19</t>
+  </si>
+  <si>
+    <t>Math write-up before any code.</t>
+  </si>
+  <si>
+    <t>Discretize (ZOH / state transition matrix), implement propagator</t>
+  </si>
+  <si>
+    <t>Unit tests: propagator vs. analytic CW solution (free-drift ellipse check)</t>
+  </si>
+  <si>
+    <t>First real test in tests/ — not optional.</t>
+  </si>
+  <si>
+    <t>Study state estimation / noise modeling basics (L5), then add Gaussian process + measurement noise to the sim, with a basic Kalman filter feeding the controller</t>
+  </si>
+  <si>
+    <t>Parallel with Task 9 tail</t>
+  </si>
+  <si>
+    <t>Without this, the whole project assumes perfect knowledge — a real weak point. If time is tight, the minimal KF can slip to just before Task 20.</t>
+  </si>
+  <si>
+    <t>Build nonlinear two-body plant (sim/) + CW-vs-nonlinear sweep over target eccentricity e and separation ρ (L20); short write-up: CW linearization assumptions &amp; validity limits</t>
+  </si>
+  <si>
+    <t>Parallel with Task 10 and start of Task 12</t>
+  </si>
+  <si>
+    <t>Goes in docs/ — one page is enough. Sweep above SL-16's e≈1e-3 is a stress test, label it as such. End date moved 9→11 Oct; Phase 2 opens with study tasks, so no critical-path impact.</t>
+  </si>
+  <si>
+    <t>Phase 2 – Linear MPC (Translational)</t>
+  </si>
+  <si>
+    <t>Study convex optimization fundamentals (L6)</t>
+  </si>
+  <si>
+    <t>Parallel with Task 13 start</t>
+  </si>
+  <si>
+    <t>Study MPC theory: receding horizon, cost design, terminal ingredients, stability intro (L7)</t>
+  </si>
+  <si>
+    <t>Formulate QP/SOCP: cost function, horizon N, thrust constraints, keep-out / approach-cone constraints (hard) — convex modeling per L21</t>
+  </si>
+  <si>
+    <t>Write the formulation doc before opening CVXPY.</t>
+  </si>
+  <si>
+    <t>Study soft constraints &amp; recursive feasibility basics (L8)</t>
+  </si>
+  <si>
+    <t>Parallel with Task 14</t>
+  </si>
+  <si>
+    <t>Extend formulation with soft constraints (slack variables) for guaranteed feasibility</t>
+  </si>
+  <si>
+    <t>Talking point #1 for the interview.</t>
+  </si>
+  <si>
+    <t>Study CVXPY practical usage (L9)</t>
+  </si>
+  <si>
+    <t>Parallel with Task 16</t>
+  </si>
+  <si>
+    <t>Implement linear MPC in CVXPY (nominal, noiseless case)</t>
+  </si>
+  <si>
+    <t>Closed-loop nominal simulation + core metrics (fuel/Δv consumption, settling time, constraint violations)</t>
+  </si>
+  <si>
+    <t>First real deliverable — usable in CV/interview from here.</t>
+  </si>
+  <si>
+    <t>Closed-loop Monte Carlo simulation under navigation noise + CW-vs-plant mismatch (dispersion plots, robustness check; L22)</t>
+  </si>
+  <si>
+    <t>Talking point #2: how the controller degrades under realistic uncertainty.</t>
+  </si>
+  <si>
+    <t>Unit tests for MPC module (feasibility checks, solver status handling)</t>
+  </si>
+  <si>
+    <t>Parallel with Task 22</t>
+  </si>
+  <si>
+    <t>Document Phase 1–2 results (plots, metrics table) in repo README/report</t>
+  </si>
+  <si>
+    <t>Parallel with Task 21</t>
+  </si>
+  <si>
+    <t>This is what you screen-share if interviewed early.</t>
+  </si>
+  <si>
+    <t>Application (parallel track)</t>
+  </si>
+  <si>
+    <t>Align motivation letter language with LA3 + shortlisted labs' recent papers</t>
+  </si>
+  <si>
+    <t>Parallel with Phase 0–1</t>
+  </si>
+  <si>
+    <t>Draft CV bullets + motivation letter using Phase 1–2 results/plots</t>
+  </si>
+  <si>
+    <t>Parallel with Phase 2 tail</t>
+  </si>
+  <si>
+    <t>MILESTONE: Submit E3 application (up to 3 lab choices, CV, transcripts, statement of purpose, ID)</t>
+  </si>
+  <si>
+    <t>Hard deadline — confirmed on eee.epfl.ch</t>
+  </si>
+  <si>
+    <t>Portal opens Oct 2026, closes Nov 1, 2026.</t>
+  </si>
+  <si>
+    <t>Keep GitHub repo continuously updated &amp; interview-ready (rolling — do not batch this at the end)</t>
+  </si>
+  <si>
+    <t>Runs in parallel with everything below</t>
+  </si>
+  <si>
+    <t>Interviews can happen any time Nov–early Mar — the repo must be presentable throughout, not just in January.</t>
+  </si>
+  <si>
+    <t>Phase 3 – Rotational Dynamics (3-DoF)</t>
+  </si>
+  <si>
+    <t>Study attitude kinematics &amp; dynamics: quaternions/MRPs, Euler's equations (L10)</t>
+  </si>
+  <si>
+    <t>Formulate nonlinear attitude dynamics</t>
+  </si>
+  <si>
+    <t>Linearize (small-angle / MRP) for use inside a linear MPC (L11)</t>
+  </si>
+  <si>
+    <t>Parallel with Task 28 tail</t>
+  </si>
+  <si>
+    <t>Unit tests: attitude propagator validation</t>
+  </si>
+  <si>
+    <t>Phase 4 – Rotational MPC</t>
+  </si>
+  <si>
+    <t>Study RW/RCS actuator constraints &amp; torque allocation basics (L12)</t>
+  </si>
+  <si>
+    <t>Formulate attitude MPC (torque/momentum saturation, soft constraints where needed)</t>
+  </si>
+  <si>
+    <t>Implement + closed-loop detumble/pointing simulation + metrics</t>
+  </si>
+  <si>
+    <t>Monte Carlo robustness test under attitude estimation noise</t>
+  </si>
+  <si>
+    <t>PORTFOLIO CHECKPOINT #1: integrate translational + rotational results into one unified report</t>
+  </si>
+  <si>
+    <t>Safe fallback deliverable if the interview happens before Phase 5 is mature.</t>
+  </si>
+  <si>
+    <t>Phase 5 – Nonlinear Coupled 6-DoF MPC</t>
+  </si>
+  <si>
+    <t>Study NMPC theory: multiple shooting, direct collocation, SQP/interior-point basics (L13)</t>
+  </si>
+  <si>
+    <t>Study CasADi practical usage + example patterns (L14)</t>
+  </si>
+  <si>
+    <t>Parallel with Task 36 tail</t>
+  </si>
+  <si>
+    <t>Study solver internals: why OSQP/ECOS for QP vs. IPOPT for NLP, warm-starting (L15)</t>
+  </si>
+  <si>
+    <t>Parallel with Task 37 / holidays</t>
+  </si>
+  <si>
+    <t>Formulate coupled nonlinear 6-DoF model (translation–rotation coupling via docking-port offset; L23)</t>
+  </si>
+  <si>
+    <t>This is the 'frontier' you present as in-progress at the interview.</t>
+  </si>
+  <si>
+    <t>Implement NMPC in CasADi (multiple shooting), first working closed-loop test case</t>
+  </si>
+  <si>
+    <t>A rough working version is enough — do not over-polish before validating it works at all.</t>
+  </si>
+  <si>
+    <t>Full validation suite: Monte Carlo over initial conditions + noise, metrics table, solver-time stats</t>
+  </si>
+  <si>
+    <t>Recursive feasibility / terminal set discussion — analytical or qualitative write-up</t>
+  </si>
+  <si>
+    <t>Parallel with Task 41 tail</t>
+  </si>
+  <si>
+    <t>Even a qualitative discussion is a strong interview talking point.</t>
+  </si>
+  <si>
+    <t>PORTFOLIO CHECKPOINT #2: full 6-DoF results integrated into repo + report</t>
+  </si>
+  <si>
+    <t>No hard deadline — extend if needed, this is research-grade work</t>
+  </si>
+  <si>
+    <t>It is fine — expected, even — for this to still be open at interview time.</t>
+  </si>
+  <si>
+    <t>Phase 6 – Stretch Goals (optional)</t>
+  </si>
+  <si>
+    <t>Study robust / tube MPC concepts (L17) — directly ties to LA3's own research</t>
+  </si>
+  <si>
+    <t>Explore a robust or tube-based MPC extension on the translational subsystem</t>
+  </si>
+  <si>
+    <t>Optional — only if Phase 5 finished with time to spare.</t>
+  </si>
+  <si>
+    <t>Optional: simple synthetic vision-based relative pose estimation module (closes the GNC sense loop; L24)</t>
+  </si>
+  <si>
+    <t>Can run parallel with Task 45</t>
+  </si>
+  <si>
+    <t>Relevant if targeting Cavallaro/LIDIAP as a lab choice — see Target Labs sheet.</t>
+  </si>
+  <si>
+    <t>Optional: learning-based MPC exploration (e.g. Gaussian process or NN model-mismatch correction; L25)</t>
+  </si>
+  <si>
+    <t>Ties back to your original AI/ML interest without abandoning the control core.</t>
+  </si>
+  <si>
+    <t>Prepare a short conference-style write-up/poster of the full project as a standalone portfolio artifact</t>
+  </si>
+  <si>
+    <t>Good to have before the internship itself starts (May–Oct 2027).</t>
+  </si>
+  <si>
+    <t>Interview Prep (parallel track)</t>
+  </si>
+  <si>
+    <t>Prepare talking points: CW → linear MPC → 6-DoF NMPC narrative, open problems, stability/feasibility discussion</t>
+  </si>
+  <si>
+    <t>Parallel with Phase 3 start — do this early, interviews can start mid-Nov</t>
+  </si>
+  <si>
+    <t>Mock technical interview (self Q&amp;A or with a peer/professor)</t>
+  </si>
+  <si>
+    <t>Repeat again in Jan/Feb if the interview hasn't happened yet.</t>
+  </si>
+  <si>
+    <t>Lab-specific Q&amp;A prep: re-read papers of whichever lab actually invites you, anticipate questions</t>
+  </si>
+  <si>
+    <t>Rolling — triggered by an actual interview invite, not a fixed date</t>
+  </si>
+  <si>
+    <t>See Target Labs sheet for the shortlist.</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>MILESTONE: E3 results communicated by EPFL</t>
+  </si>
+  <si>
+    <t>Confirm exact date on eee.epfl.ch — currently 'around mid-March 2027' per official FAQ.</t>
+  </si>
+  <si>
+    <t>Legend:</t>
+  </si>
+  <si>
+    <t>Shaded rows = milestones/deadlines (fixed dates, not flexible tasks)</t>
+  </si>
+  <si>
+    <t>Progress summary:</t>
+  </si>
+  <si>
+    <t>Tasks done</t>
+  </si>
+  <si>
+    <t>Tasks in progress</t>
+  </si>
+  <si>
+    <t>Tasks not started</t>
+  </si>
+  <si>
+    <t>% complete</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Needed For (Project Task)</t>
+  </si>
+  <si>
+    <t>Study By Date</t>
+  </si>
+  <si>
+    <t>Resource(s)</t>
+  </si>
+  <si>
+    <t>Git &amp; GitHub fundamentals: init, add, commit, push, .gitignore, README, basic branching</t>
+  </si>
+  <si>
+    <t>Task 1 (repo setup) — before writing any project code</t>
+  </si>
+  <si>
+    <t>GitHub's official 'Hello World' guide (docs.github.com); Git Handbook / Pro Git book ch. 1–2 (free, git-scm.com/book)</t>
+  </si>
+  <si>
+    <t>Python fundamentals for MATLAB users: syntax, NumPy arrays &amp; 0-based indexing, functions, control flow, list/dict basics</t>
+  </si>
+  <si>
+    <t>Task 3 (environment setup) and everything after — first time using Python</t>
+  </si>
+  <si>
+    <t>NumPy official 'NumPy for MATLAB users' guide (numpy.org); Python official tutorial ch. 3–4 (docs.python.org)</t>
+  </si>
+  <si>
+    <t>Linear systems &amp; state-space representation (A, B matrices, controllability), matrix exponential, forced response (variation-of-constants formula)</t>
+  </si>
+  <si>
+    <t>Task 7 (CW state-space formulation)</t>
+  </si>
+  <si>
+    <t>Åström &amp; Murray, 'Feedback Systems': ch. 5 (linear systems: matrix exponential, convolution/forced response) and §6.1 (reachability); ch. 2–4 as background only. Verify numbering against your edition. Second source: Wie §2.5 (Modern State-Space Methods) and §1.3. Or your intro control course notes.</t>
+  </si>
+  <si>
+    <t>Clohessy-Wiltshire equations: derivation, assumptions, forced response with control acceleration, ZOH discretization (A_d, B_d), impulsive vs. continuous thrust</t>
+  </si>
+  <si>
+    <t>Tasks 7–8 (CW model + discretization); Task 6 (study)</t>
+  </si>
+  <si>
+    <t>Curtis ch. 7 §7.4 (CW equations, state transition matrix Φ — homogeneous solution only, no control input); Wie §4.6 (Orbital Rendezvous) for CW. Wie §2.4 (ZOH) is Laplace-domain only — skip it. ZOH / sampling with input: Åström &amp; Wittenmark 'Computer-Controlled Systems' (sampling of continuous-time systems) or, preferred, Franklin, Powell &amp; Workman 'Digital Control of Dynamic Systems': §4.3.3 (state-space form of the ZOH discretization, Φ and Γ) and §4.3.5 (numerical computation of Φ and Γ). Their Φ, Γ = your A_d, B_d. Skip the z-transform sections. Practice: expm of augmented matrix [[A,B],[0,0]]·dt, check vs. closed-form Φ.</t>
+  </si>
+  <si>
+    <t>State estimation &amp; noise modeling basics: process/measurement noise, discrete Kalman filter (implement the LTI case so the MPC acts on an estimated state)</t>
+  </si>
+  <si>
+    <t>Task 10 (adding realistic navigation uncertainty)</t>
+  </si>
+  <si>
+    <t>Simon, 'Optimal State Estimation', ch. 1–5 (or any intro Kalman filter tutorial, e.g. Welch &amp; Bishop's classic KF tutorial, UNC). Practice: write a 6-state KF on the CW model.</t>
+  </si>
+  <si>
+    <t>Convex optimization fundamentals: convex sets/functions, QP structure, why convexity matters for solvers</t>
+  </si>
+  <si>
+    <t>Task 14 (QP formulation for linear MPC)</t>
+  </si>
+  <si>
+    <t>Boyd &amp; Vandenberghe, 'Convex Optimization', ch. 1–4 (free PDF); Stanford EE364a lecture videos</t>
+  </si>
+  <si>
+    <t>MPC theory: receding horizon principle, cost function design, prediction matrices (condensed vs. sparse formulation), LQR / DARE for the terminal cost, terminal set, stability intro</t>
+  </si>
+  <si>
+    <t>Tasks 14, 18–19 (Linear MPC formulation + implementation)</t>
+  </si>
+  <si>
+    <t>Rawlings, Mayne &amp; Diehl, 'Model Predictive Control: Theory, Computation, and Design' (free PDF), ch. 1–2 (ch. 1 has the LQR/prediction-matrix material). Practice: scipy.linalg.solve_discrete_are for P; compare unconstrained MPC with LQR as a sanity check.</t>
+  </si>
+  <si>
+    <t>Soft constraints &amp; recursive feasibility in MPC (slack variables, exact penalty functions)</t>
+  </si>
+  <si>
+    <t>Task 16 (soft-constrained MPC)</t>
+  </si>
+  <si>
+    <t>Rawlings/Mayne/Diehl ch. 2 (constraint handling) + ch. 3 intro; Kerrigan &amp; Maciejowski, 'Soft constraints and exact penalty functions in MPC' (paper, freely searchable). Study-by moved from 23 Oct to 21 Oct: Task 16 starts 21 Oct.</t>
+  </si>
+  <si>
+    <t>CVXPY practical usage: problem setup, parameters vs. variables, solving MPC in a loop</t>
+  </si>
+  <si>
+    <t>Task 18 (Linear MPC implementation)</t>
+  </si>
+  <si>
+    <t>cvxpy.org official tutorial + examples gallery (MPC example specifically)</t>
+  </si>
+  <si>
+    <t>Attitude kinematics &amp; dynamics: quaternions or MRPs, Euler's rotational equations of motion</t>
+  </si>
+  <si>
+    <t>Task 27–28 (rotational dynamics formulation)</t>
+  </si>
+  <si>
+    <t>Schaub &amp; Junkins, 'Analytical Mechanics of Space Systems', ch. 3–4; Wie ch. 5 (§5.4 quaternions, §5.5 kinematic differential equations) and ch. 6 (§6.4 Euler's rotational equations, §6.10 rigid body in a circular orbit).</t>
+  </si>
+  <si>
+    <t>Linearization techniques for attitude models (small-angle, MRP linearization) for use inside a linear MPC</t>
+  </si>
+  <si>
+    <t>Task 29 (linearized attitude state-space model)</t>
+  </si>
+  <si>
+    <t>Schaub &amp; Junkins ch. 4; Wie ch. 5 (kinematics, for the linearization) and §7.3 (quaternion-feedback reorientation, as classical baseline vs. the MPC).</t>
+  </si>
+  <si>
+    <t>Reaction wheel / RCS actuator constraints: torque/momentum saturation, allocation basics</t>
+  </si>
+  <si>
+    <t>Task 31–32 (rotational MPC with actuator constraints)</t>
+  </si>
+  <si>
+    <t>Wie, 'Space Vehicle Dynamics and Control': §7.4 (attitude control and momentum management: wheel torque/momentum saturation), §7.6 (optimal jet selection logic, for RCS allocation). §7.5 (CMG) not needed.</t>
+  </si>
+  <si>
+    <t>Nonlinear programming for control: direct multiple shooting, collocation, SQP/interior-point basics</t>
+  </si>
+  <si>
+    <t>Tasks 36, 39 (NMPC formulation)</t>
+  </si>
+  <si>
+    <t>Diehl &amp; Gros, 'Numerical Optimal Control' (free PDF, syscop.de); Rawlings/Mayne/Diehl ch. 8</t>
+  </si>
+  <si>
+    <t>CasADi practical usage: symbolic modeling, nlpsol, multiple-shooting implementation pattern</t>
+  </si>
+  <si>
+    <t>Task 40 (NMPC implementation)</t>
+  </si>
+  <si>
+    <t>casadi.org 'Getting started' + official example pack (rocket/robot MPC examples)</t>
+  </si>
+  <si>
+    <t>Solver internals: QP solvers (OSQP, ECOS) vs. NLP solvers (IPOPT), warm-starting, why the choice matters</t>
+  </si>
+  <si>
+    <t>Tasks 38, 40 — and a common interview question</t>
+  </si>
+  <si>
+    <t>OSQP paper (Stellato et al., free); IPOPT documentation intro; CasADi docs section on solver plugins</t>
+  </si>
+  <si>
+    <t>MPC stability &amp; recursive feasibility in depth (Lyapunov-based terminal ingredients) + invariant sets / terminal set computation</t>
+  </si>
+  <si>
+    <t>Task 42 + Task 49 (interview talking points)</t>
+  </si>
+  <si>
+    <t>Rawlings/Mayne/Diehl, ch. 2–3 (stability chapters) — read a first pass early (by mid-Nov) since interviews can start then; revisit before Task 42. Invariant sets: Blanchini &amp; Miani, 'Set-Theoretic Methods in Control' (recognize the vocabulary); MPT3 toolbox docs (mpt3.org) for intuition on invariant-set computation.</t>
+  </si>
+  <si>
+    <t>Robust / tube MPC — conceptual overview (Prof. Jones' group works on this; recognize the vocabulary)</t>
+  </si>
+  <si>
+    <t>Task 44 + interview talking points</t>
+  </si>
+  <si>
+    <t>Rawlings/Mayne/Diehl ch. 3 (robust MPC section); skim 2–3 recent LA3 (Colin Jones) papers on epfl.ch/labs/la3. Study-by moved from 20 Nov to 15 Oct: the conceptual pass has to feed the motivation letter (Task 23, 1–15 Oct) and the 1 Nov submission. Refine in Phase 6.</t>
+  </si>
+  <si>
+    <t>Scientific Python toolkit &amp; testing: matplotlib for report-quality plots, SciPy (linalg.expm, integrate.solve_ivp), pytest + numpy.testing.assert_allclose (tolerances), Jupyter workflow</t>
+  </si>
+  <si>
+    <t>Tasks 3, 8, 9, 21 (first code + first tests in tests/)</t>
+  </si>
+  <si>
+    <t>matplotlib official tutorials ('Quick start'); SciPy docs for scipy.linalg.expm and scipy.integrate.solve_ivp; pytest 'Get started' (docs.pytest.org); NumPy docs for numpy.testing.</t>
+  </si>
+  <si>
+    <t>Technical documentation: LaTeX (or Markdown with math) for formulation docs, equation/figure conventions, README structure</t>
+  </si>
+  <si>
+    <t>Tasks 7, 11, 14, 22, 35 (math write-ups before code)</t>
+  </si>
+  <si>
+    <t>Overleaf 'Learn LaTeX in 30 minutes' + amsmath basics; or GitHub docs on math in Markdown. Half a day is enough.</t>
+  </si>
+  <si>
+    <t>Nonlinear relative dynamics &amp; numerical propagation: inertial two-body propagation, inertial→LVLH transform of the relative state, effect of target eccentricity, J2 / differential drag as optional plant perturbations (plant vs. controller-model mismatch)</t>
+  </si>
+  <si>
+    <t>Tasks 9, 11, 20 (nonlinear plant, CW-vs-nonlinear sweep, Monte Carlo mismatch)</t>
+  </si>
+  <si>
+    <t>Curtis ch. 7 §7.2 (nonlinear relative motion equations); Wie §3.6 (orbital perturbations) or Vallado, 'Fundamentals of Astrodynamics and Applications' — only for the optional terms; SciPy solve_ivp docs (rtol/atol choice).</t>
+  </si>
+  <si>
+    <t>Convex modeling of MPC constraints &amp; costs: second-order cone constraints, ‖u‖₂ ≤ u_max vs. box limits, L1/L2 fuel-cost norms vs. quadratic cost, approach cone / line-of-sight as SOC, convexifying the keep-out zone, slack penalties</t>
+  </si>
+  <si>
+    <t>Tasks 14, 16 (constraint set of the QP/SOCP)</t>
+  </si>
+  <si>
+    <t>Boyd &amp; Vandenberghe ch. 4 (§4.4: QP and SOCP); CVXPY docs, 'Disciplined Convex Programming' page; rendezvous-MPC papers collected in Task 4 (e.g. Hartley et al., 'Model predictive control system design and implementation for spacecraft rendezvous', Control Eng. Practice, 2012 — verify).</t>
+  </si>
+  <si>
+    <t>Monte Carlo methodology: sampling initial conditions &amp; noise, seeded reproducibility (numpy.random.Generator), dispersion/percentile metrics, number of runs vs. confidence, reporting constraint-violation rates</t>
+  </si>
+  <si>
+    <t>Tasks 20, 34, 41 (robustness studies)</t>
+  </si>
+  <si>
+    <t>NumPy docs, 'Random Generator'; copy the dispersion-reporting conventions from the papers read in Task 4.</t>
+  </si>
+  <si>
+    <t>6-DoF coupling kinematics: docking-port lever arm (r_dock = r_cm + R·b), velocity/acceleration of an offset point, torques from off-axis thrust, relative pose in LVLH, unit-quaternion norm handling in NMPC</t>
+  </si>
+  <si>
+    <t>Task 39 (coupled 6-DoF model)</t>
+  </si>
+  <si>
+    <t>Schaub &amp; Junkins ch. 3–4 (rigid-body kinematics, revisit); Wie ch. 5–6 (kinematics + rigid-body dynamics, §6.10 for the orbit coupling) and §7.4/§7.6 (actuators); Fehse, 'Automated Rendezvous and Docking of Spacecraft' (Cambridge, 2003); coupled 6-DoF MPC papers for proximity operations (collect in Task 37).</t>
+  </si>
+  <si>
+    <t>OPTIONAL — Vision-based relative pose estimation: pinhole camera model, PnP / feature-based pose from a known 3D model, pose uncertainty</t>
+  </si>
+  <si>
+    <t>Task 46 (optional stretch)</t>
+  </si>
+  <si>
+    <t>Hartley &amp; Zisserman, 'Multiple View Geometry in Computer Vision', ch. 6 (camera models) — verify; OpenCV solvePnP tutorial (docs.opencv.org).</t>
+  </si>
+  <si>
+    <t>OPTIONAL — Learning-based MPC: Gaussian-process regression, model-mismatch correction inside MPC, safety via constraint tightening</t>
+  </si>
+  <si>
+    <t>Task 47 (optional stretch)</t>
+  </si>
+  <si>
+    <t>Rasmussen &amp; Williams, 'Gaussian Processes for Machine Learning', ch. 2 (free PDF); Hewing et al., 'Learning-based model predictive control: toward safe learning in control', Annu. Rev. Control Robot. Auton. Syst., 2020 — verify.</t>
+  </si>
+  <si>
+    <t>Topics done</t>
+  </si>
+  <si>
+    <t>Topics in progress</t>
+  </si>
+  <si>
+    <t>Topics not started</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Professor</t>
+  </si>
+  <si>
+    <t>Lab</t>
+  </si>
+  <si>
+    <t>Research Areas (from EPFL listing)</t>
+  </si>
+  <si>
+    <t>Why It Fits This Project</t>
+  </si>
+  <si>
+    <t>Fit Level</t>
+  </si>
+  <si>
+    <t>Colin Jones</t>
+  </si>
+  <si>
+    <t>Automatic Control Laboratory 3 (LA3)</t>
+  </si>
+  <si>
+    <t>Control Systems, Optimization, Robotics &amp; Autonomous Systems, Learning &amp; Decision Systems</t>
+  </si>
+  <si>
+    <t>MPC is literally their core research output. Your CW→linear MPC→6-DoF NMPC roadmap is a direct, self-contained application case study of what this lab does daily.</t>
+  </si>
+  <si>
+    <t>PRIMARY</t>
+  </si>
+  <si>
+    <t>Maryam Kamgarpour</t>
+  </si>
+  <si>
+    <t>Systems Control and Multiagent Optimization Research</t>
+  </si>
+  <si>
+    <t>Learning &amp; Decision Systems, Robotics and Autonomous Systems</t>
+  </si>
+  <si>
+    <t>Optimization-under-constraints is the exact spine of your QP/NMPC formulation work — strong second choice inside the same sub-field as Jones, not a dilution of your pitch.</t>
+  </si>
+  <si>
+    <t>STRONG</t>
+  </si>
+  <si>
+    <t>Alireza Karimi</t>
+  </si>
+  <si>
+    <t>Data-Driven Modelling and Control Group</t>
+  </si>
+  <si>
+    <t>Data &amp; Network Sciences, Energy Systems, Learning &amp; Decision Systems, Robotics, Theory and Simulation</t>
+  </si>
+  <si>
+    <t>System identification + robust control. Your noise-robustness testing (Monte Carlo under navigation uncertainty) speaks directly to what this group cares about.</t>
+  </si>
+  <si>
+    <t>Giancarlo Ferrari Trecate</t>
+  </si>
+  <si>
+    <t>Dependable Control and Decision group (DECAR)</t>
+  </si>
+  <si>
+    <t>Learning &amp; Decision Systems, Mechanical Engineering, Energy Systems</t>
+  </si>
+  <si>
+    <t>Distributed/robust control theory overlaps with your feasibility and soft-constraint work. Note from earlier discussion: PI has an Italian academic background (Pavia/Polimi-adjacent), which may make your 110L and rigor easier to contextualize.</t>
+  </si>
+  <si>
+    <t>Andrea Cavallaro</t>
+  </si>
+  <si>
+    <t>LIDIAP</t>
+  </si>
+  <si>
+    <t>Imaging &amp; Vision, Learning &amp; Decision Systems, Robotics and Autonomous Systems, Sports Technology</t>
+  </si>
+  <si>
+    <t>Relevant only if you build the optional Phase 6 vision/pose-estimation stretch goal (Task 46) — that closes the 'Sense' half of the GNC loop for a non-cooperative target. Weaker fit if you stay purely on the control side.</t>
+  </si>
+  <si>
+    <t>MODERATE</t>
+  </si>
+  <si>
+    <t>Anja Skrivervik</t>
+  </si>
+  <si>
+    <t>SCI STI AS Group</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Flexible Electronics, Personalized Health, Robotics and Autonomous Systems, Space Technology</t>
+  </si>
+  <si>
+    <t>Explicit Space Technology tag — useful if you want to keep the ADR framing front-and-center rather than pivoting the pitch fully toward generic autonomous systems. Verify current project focus before listing.</t>
+  </si>
+  <si>
+    <t>Farhad Rachidi-Haeri</t>
+  </si>
+  <si>
+    <t>SCI STI FR Group</t>
+  </si>
+  <si>
+    <t>Electrical Engineering, Energy Systems, Space Technology</t>
+  </si>
+  <si>
+    <t>Space Technology tag present, but the group's recent work may skew toward EM/energy rather than GNC — check the lab's current project list on epfl.ch before including as one of your 3 choices.</t>
+  </si>
+  <si>
+    <t>MODERATE (verify first)</t>
+  </si>
+  <si>
+    <t>Note on the E3 application form:</t>
+  </si>
+  <si>
+    <t>The E3 form asks for up to 3 lab choices. Recommended combination given your project: 1) Colin Jones (LA3) — primary; 2) Kamgarpour or Karimi — same control/optimization core, not a dilution of the pitch; 3) Ferrari Trecate — still control theory, different flavor (distributed/robust). Keep all 3 inside control &amp; optimization rather than mixing in a vision or space-hardware lab, so the motivation letter tells one coherent story.</t>
+  </si>
+  <si>
+    <t>Beyond E3 (separate processes, same project transfers directly):</t>
+  </si>
+  <si>
+    <t>ETH Zürich Robotics Student Summer Fellowship — Robotic Systems Lab (Hutter) or Autonomous Systems Lab (Siegwart). Not part of E3; separate application process and deadline (check ethz.ch directly). Your 6-DoF MPC ADR project is an equally strong pitch there, since both labs value real-time optimization-based control on physical/simulated systems. If E3 doesn't work out, a direct email to a PhD student in either lab (proposing a Master Thesis) is also a standard, lower-barrier path in — worth keeping as a parallel option rather than waiting for E3 results in March.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="d\-mmm\-yy"/>
-    <numFmt numFmtId="166" formatCode="0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d\-mmm\-yy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -810,39 +824,21 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -867,14 +863,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -890,110 +886,54 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1007,11 +947,33 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1070,47 +1032,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1118,12 +1096,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1152,7 +1130,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1173,7 +1151,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1224,7 +1202,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1242,33 +1220,32 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="40"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1297,8 +1274,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1307,14 +1284,14 @@
       <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="6">
         <v>46288</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="6">
         <v>46289</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <f aca="false">E2-D2</f>
+      <c r="F2" s="3">
+        <f t="shared" ref="F2:F33" si="0">E2-D2</f>
         <v>1</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -1327,8 +1304,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1337,28 +1314,28 @@
       <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="6">
         <v>46288</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="6">
         <v>46292</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <f aca="false">E3-D3</f>
+      <c r="F3" s="3">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1367,14 +1344,14 @@
       <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="6">
         <v>46289</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="6">
         <v>46291</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <f aca="false">E4-D4</f>
+      <c r="F4" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G4" s="5" t="s">
@@ -1385,8 +1362,8 @@
       </c>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1395,14 +1372,14 @@
       <c r="C5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="6">
         <v>46288</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="6">
         <v>46297</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <f aca="false">E5-D5</f>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="G5" s="5" t="s">
@@ -1415,8 +1392,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1425,26 +1402,26 @@
       <c r="C6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="6">
         <v>46288</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="6">
         <v>46293</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <f aca="false">E6-D6</f>
+      <c r="F6" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1453,26 +1430,26 @@
       <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="6">
         <v>46291</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="6">
         <v>46298</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <f aca="false">E7-D7</f>
+      <c r="F7" s="3">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+    <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1481,28 +1458,28 @@
       <c r="C8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="6">
         <v>46294</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="6">
         <v>46298</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <f aca="false">E8-D8</f>
+      <c r="F8" s="3">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+    <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -1511,26 +1488,26 @@
       <c r="C9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="6">
         <v>46298</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="6">
         <v>46301</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <f aca="false">E9-D9</f>
+      <c r="F9" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+    <row r="10" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1539,14 +1516,14 @@
       <c r="C10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="6">
         <v>46301</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="6">
         <v>46303</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <f aca="false">E10-D10</f>
+      <c r="F10" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G10" s="5" t="s">
@@ -1559,8 +1536,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+    <row r="11" spans="1:9" ht="39.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1569,14 +1546,14 @@
       <c r="C11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="6">
         <v>46301</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="6">
         <v>46304</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <f aca="false">E11-D11</f>
+      <c r="F11" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G11" s="5" t="s">
@@ -1589,8 +1566,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+    <row r="12" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -1599,14 +1576,14 @@
       <c r="C12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="6">
         <v>46303</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="6">
         <v>46306</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <f aca="false">E12-D12</f>
+      <c r="F12" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G12" s="5" t="s">
@@ -1619,8 +1596,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1629,14 +1606,14 @@
       <c r="C13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="6">
         <v>46304</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="6">
         <v>46308</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <f aca="false">E13-D13</f>
+      <c r="F13" s="3">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G13" s="5" t="s">
@@ -1647,8 +1624,8 @@
       </c>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+    <row r="14" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1657,14 +1634,14 @@
       <c r="C14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="6">
         <v>46307</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="6">
         <v>46313</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <f aca="false">E14-D14</f>
+      <c r="F14" s="3">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="G14" s="5" t="s">
@@ -1675,8 +1652,8 @@
       </c>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+    <row r="15" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1685,14 +1662,14 @@
       <c r="C15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="6">
         <v>46313</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="6">
         <v>46316</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <f aca="false">E15-D15</f>
+      <c r="F15" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G15" s="5" t="s">
@@ -1705,8 +1682,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1715,14 +1692,14 @@
       <c r="C16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="6">
         <v>46313</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="6">
         <v>46318</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <f aca="false">E16-D16</f>
+      <c r="F16" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="G16" s="5" t="s">
@@ -1733,8 +1710,8 @@
       </c>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+    <row r="17" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -1743,14 +1720,14 @@
       <c r="C17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="6">
         <v>46316</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="6">
         <v>46318</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <f aca="false">E17-D17</f>
+      <c r="F17" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G17" s="5" t="s">
@@ -1763,8 +1740,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+    <row r="18" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -1773,14 +1750,14 @@
       <c r="C18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="6">
         <v>46316</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="6">
         <v>46318</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <f aca="false">E18-D18</f>
+      <c r="F18" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G18" s="5" t="s">
@@ -1791,8 +1768,8 @@
       </c>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+    <row r="19" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -1801,14 +1778,14 @@
       <c r="C19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="6">
         <v>46318</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="6">
         <v>46321</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <f aca="false">E19-D19</f>
+      <c r="F19" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G19" s="5" t="s">
@@ -1819,8 +1796,8 @@
       </c>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+    <row r="20" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -1829,14 +1806,14 @@
       <c r="C20" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="6">
         <v>46321</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="6">
         <v>46323</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <f aca="false">E20-D20</f>
+      <c r="F20" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G20" s="5" t="s">
@@ -1849,8 +1826,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
+    <row r="21" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -1859,14 +1836,14 @@
       <c r="C21" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="6">
         <v>46323</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="6">
         <v>46325</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <f aca="false">E21-D21</f>
+      <c r="F21" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G21" s="5" t="s">
@@ -1879,8 +1856,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
+    <row r="22" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -1889,14 +1866,14 @@
       <c r="C22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="6">
         <v>46325</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="6">
         <v>46326</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <f aca="false">E22-D22</f>
+      <c r="F22" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G22" s="5" t="s">
@@ -1907,8 +1884,8 @@
       </c>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
+    <row r="23" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -1917,14 +1894,14 @@
       <c r="C23" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="6">
         <v>46325</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="6">
         <v>46327</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <f aca="false">E23-D23</f>
+      <c r="F23" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G23" s="5" t="s">
@@ -1937,8 +1914,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
+    <row r="24" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -1947,14 +1924,14 @@
       <c r="C24" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="6">
         <v>46296</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="6">
         <v>46310</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <f aca="false">E24-D24</f>
+      <c r="F24" s="3">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="G24" s="5" t="s">
@@ -1965,8 +1942,8 @@
       </c>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
+    <row r="25" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -1975,14 +1952,14 @@
       <c r="C25" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="6">
         <v>46311</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="6">
         <v>46323</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <f aca="false">E25-D25</f>
+      <c r="F25" s="3">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="G25" s="5" t="s">
@@ -1993,8 +1970,8 @@
       </c>
       <c r="I25" s="5"/>
     </row>
-    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
+    <row r="26" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7">
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -2003,14 +1980,14 @@
       <c r="C26" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="10">
         <v>46327</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="10">
         <v>46327</v>
       </c>
-      <c r="F26" s="7" t="n">
-        <f aca="false">E26-D26</f>
+      <c r="F26" s="7">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G26" s="9" t="s">
@@ -2023,8 +2000,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
+    <row r="27" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -2033,14 +2010,14 @@
       <c r="C27" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="6">
         <v>46327</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="6">
         <v>46447</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <f aca="false">E27-D27</f>
+      <c r="F27" s="3">
+        <f t="shared" si="0"/>
         <v>120</v>
       </c>
       <c r="G27" s="5" t="s">
@@ -2053,8 +2030,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
+    <row r="28" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -2063,14 +2040,14 @@
       <c r="C28" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="6">
         <v>46327</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="6">
         <v>46334</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <f aca="false">E28-D28</f>
+      <c r="F28" s="3">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="G28" s="5" t="s">
@@ -2081,8 +2058,8 @@
       </c>
       <c r="I28" s="5"/>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
+    <row r="29" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -2091,14 +2068,14 @@
       <c r="C29" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="6">
         <v>46334</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="6">
         <v>46338</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <f aca="false">E29-D29</f>
+      <c r="F29" s="3">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G29" s="5" t="s">
@@ -2109,8 +2086,8 @@
       </c>
       <c r="I29" s="5"/>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
+    <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -2119,14 +2096,14 @@
       <c r="C30" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="6">
         <v>46336</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="6">
         <v>46339</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <f aca="false">E30-D30</f>
+      <c r="F30" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G30" s="5" t="s">
@@ -2137,8 +2114,8 @@
       </c>
       <c r="I30" s="5"/>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
+    <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -2147,14 +2124,14 @@
       <c r="C31" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="6">
         <v>46339</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="6">
         <v>46340</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <f aca="false">E31-D31</f>
+      <c r="F31" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G31" s="5" t="s">
@@ -2165,8 +2142,8 @@
       </c>
       <c r="I31" s="5"/>
     </row>
-    <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="n">
+    <row r="32" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -2175,14 +2152,14 @@
       <c r="C32" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="6">
         <v>46340</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="6">
         <v>46346</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <f aca="false">E32-D32</f>
+      <c r="F32" s="3">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="G32" s="5" t="s">
@@ -2193,8 +2170,8 @@
       </c>
       <c r="I32" s="5"/>
     </row>
-    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="n">
+    <row r="33" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -2203,14 +2180,14 @@
       <c r="C33" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="6">
         <v>46346</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="6">
         <v>46350</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <f aca="false">E33-D33</f>
+      <c r="F33" s="3">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G33" s="5" t="s">
@@ -2221,8 +2198,8 @@
       </c>
       <c r="I33" s="5"/>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="n">
+    <row r="34" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -2231,14 +2208,14 @@
       <c r="C34" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="6">
         <v>46350</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="6">
         <v>46354</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <f aca="false">E34-D34</f>
+      <c r="F34" s="3">
+        <f t="shared" ref="F34:F65" si="1">E34-D34</f>
         <v>4</v>
       </c>
       <c r="G34" s="5" t="s">
@@ -2249,8 +2226,8 @@
       </c>
       <c r="I34" s="5"/>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="n">
+    <row r="35" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -2259,14 +2236,14 @@
       <c r="C35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="6">
         <v>46354</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="6">
         <v>46357</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <f aca="false">E35-D35</f>
+      <c r="F35" s="3">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G35" s="5" t="s">
@@ -2277,8 +2254,8 @@
       </c>
       <c r="I35" s="5"/>
     </row>
-    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="n">
+    <row r="36" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="7">
         <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -2287,14 +2264,14 @@
       <c r="C36" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="10">
         <v>46357</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="10">
         <v>46360</v>
       </c>
-      <c r="F36" s="7" t="n">
-        <f aca="false">E36-D36</f>
+      <c r="F36" s="7">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G36" s="9" t="s">
@@ -2307,8 +2284,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="n">
+    <row r="37" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -2317,14 +2294,14 @@
       <c r="C37" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="6">
         <v>46360</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="6">
         <v>46371</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <f aca="false">E37-D37</f>
+      <c r="F37" s="3">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="G37" s="5" t="s">
@@ -2335,8 +2312,8 @@
       </c>
       <c r="I37" s="5"/>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="n">
+    <row r="38" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -2345,14 +2322,14 @@
       <c r="C38" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="6">
         <v>46366</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="6">
         <v>46376</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <f aca="false">E38-D38</f>
+      <c r="F38" s="3">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="G38" s="5" t="s">
@@ -2363,8 +2340,8 @@
       </c>
       <c r="I38" s="5"/>
     </row>
-    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="n">
+    <row r="39" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -2373,14 +2350,14 @@
       <c r="C39" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="6">
         <v>46371</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="6">
         <v>46392</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <f aca="false">E39-D39</f>
+      <c r="F39" s="3">
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="G39" s="5" t="s">
@@ -2391,8 +2368,8 @@
       </c>
       <c r="I39" s="5"/>
     </row>
-    <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="n">
+    <row r="40" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -2401,14 +2378,14 @@
       <c r="C40" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="6">
         <v>46392</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="6">
         <v>46402</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <f aca="false">E40-D40</f>
+      <c r="F40" s="3">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="G40" s="5" t="s">
@@ -2421,8 +2398,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="n">
+    <row r="41" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -2431,14 +2408,14 @@
       <c r="C41" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="6">
         <v>46402</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="6">
         <v>46419</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <f aca="false">E41-D41</f>
+      <c r="F41" s="3">
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="G41" s="5" t="s">
@@ -2451,8 +2428,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="n">
+    <row r="42" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -2461,14 +2438,14 @@
       <c r="C42" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="6">
         <v>46419</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="6">
         <v>46430</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <f aca="false">E42-D42</f>
+      <c r="F42" s="3">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="G42" s="5" t="s">
@@ -2479,8 +2456,8 @@
       </c>
       <c r="I42" s="5"/>
     </row>
-    <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="n">
+    <row r="43" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -2489,14 +2466,14 @@
       <c r="C43" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="6">
         <v>46428</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="6">
         <v>46436</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <f aca="false">E43-D43</f>
+      <c r="F43" s="3">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="G43" s="5" t="s">
@@ -2509,8 +2486,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="n">
+    <row r="44" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="7">
         <v>43</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -2519,14 +2496,14 @@
       <c r="C44" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="10">
         <v>46436</v>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E44" s="10">
         <v>46443</v>
       </c>
-      <c r="F44" s="7" t="n">
-        <f aca="false">E44-D44</f>
+      <c r="F44" s="7">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="G44" s="9" t="s">
@@ -2539,8 +2516,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="n">
+    <row r="45" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -2549,14 +2526,14 @@
       <c r="C45" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="6">
         <v>46443</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="6">
         <v>46456</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <f aca="false">E45-D45</f>
+      <c r="F45" s="3">
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="G45" s="5" t="s">
@@ -2567,8 +2544,8 @@
       </c>
       <c r="I45" s="5"/>
     </row>
-    <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="n">
+    <row r="46" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -2577,14 +2554,14 @@
       <c r="C46" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="6">
         <v>46456</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="6">
         <v>46470</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <f aca="false">E46-D46</f>
+      <c r="F46" s="3">
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="G46" s="5" t="s">
@@ -2597,8 +2574,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="n">
+    <row r="47" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -2607,14 +2584,14 @@
       <c r="C47" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="6">
         <v>46470</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="6">
         <v>46487</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <f aca="false">E47-D47</f>
+      <c r="F47" s="3">
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="G47" s="5" t="s">
@@ -2627,8 +2604,8 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="n">
+    <row r="48" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -2637,14 +2614,14 @@
       <c r="C48" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="6">
         <v>46487</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="6">
         <v>46507</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <f aca="false">E48-D48</f>
+      <c r="F48" s="3">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="G48" s="5" t="s">
@@ -2657,8 +2634,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="n">
+    <row r="49" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="3">
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -2667,14 +2644,14 @@
       <c r="C49" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="6">
         <v>46507</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="6">
         <v>46522</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <f aca="false">E49-D49</f>
+      <c r="F49" s="3">
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="G49" s="5" t="s">
@@ -2687,8 +2664,8 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="n">
+    <row r="50" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="3">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -2697,14 +2674,14 @@
       <c r="C50" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="6">
         <v>46327</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="6">
         <v>46341</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <f aca="false">E50-D50</f>
+      <c r="F50" s="3">
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="G50" s="5" t="s">
@@ -2715,8 +2692,8 @@
       </c>
       <c r="I50" s="5"/>
     </row>
-    <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="n">
+    <row r="51" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="3">
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -2725,14 +2702,14 @@
       <c r="C51" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="6">
         <v>46341</v>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="6">
         <v>46348</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <f aca="false">E51-D51</f>
+      <c r="F51" s="3">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="G51" s="5" t="s">
@@ -2745,8 +2722,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="n">
+    <row r="52" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="3">
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -2755,14 +2732,14 @@
       <c r="C52" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="6">
         <v>46348</v>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" s="6">
         <v>46447</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <f aca="false">E52-D52</f>
+      <c r="F52" s="3">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="G52" s="5" t="s">
@@ -2775,8 +2752,8 @@
         <v>121</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="n">
+    <row r="53" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="7">
         <v>52</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -2785,14 +2762,14 @@
       <c r="C53" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D53" s="10" t="n">
+      <c r="D53" s="10">
         <v>46461</v>
       </c>
-      <c r="E53" s="10" t="n">
+      <c r="E53" s="10">
         <v>46461</v>
       </c>
-      <c r="F53" s="7" t="n">
-        <f aca="false">E53-D53</f>
+      <c r="F53" s="7">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G53" s="9" t="s">
@@ -2805,102 +2782,94 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="12" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C59" s="13" t="n">
-        <f aca="false">COUNTIF(H2:H53,"Done")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C59" s="13">
+        <f>COUNTIF(H2:H53,"Done")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C60" s="13" t="n">
-        <f aca="false">COUNTIF(H2:H53,"In progress")</f>
+      <c r="C60" s="13">
+        <f>COUNTIF(H2:H53,"In progress")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="13" t="n">
-        <f aca="false">COUNTIF(H2:H53,"Not started")</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C61" s="13">
+        <f>COUNTIF(H2:H53,"Not started")</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="14" t="n">
-        <f aca="false">C59/COUNTA(H2:H53)</f>
-        <v>0.0384615384615385</v>
+      <c r="C62" s="14">
+        <f>C59/COUNTA(H2:H53)</f>
+        <v>0.11538461538461539</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"Not started"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H53" type="list">
+    <dataValidation type="list" sqref="H2:H53" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not started,In progress,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2920,8 +2889,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2930,7 +2899,7 @@
       <c r="C2" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="6">
         <v>46289</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2940,8 +2909,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -2950,7 +2919,7 @@
       <c r="C3" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="6">
         <v>46292</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -2960,8 +2929,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -2970,7 +2939,7 @@
       <c r="C4" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="6">
         <v>46293</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -2980,8 +2949,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="172.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:6" ht="172.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -2990,7 +2959,7 @@
       <c r="C5" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="6">
         <v>46298</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -3000,8 +2969,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -3010,7 +2979,7 @@
       <c r="C6" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="6">
         <v>46303</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -3020,8 +2989,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -3030,7 +2999,7 @@
       <c r="C7" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="6">
         <v>46308</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -3040,8 +3009,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+    <row r="8" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -3050,7 +3019,7 @@
       <c r="C8" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="6">
         <v>46313</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -3060,8 +3029,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+    <row r="9" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -3070,7 +3039,7 @@
       <c r="C9" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="6">
         <v>46316</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -3080,8 +3049,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -3090,7 +3059,7 @@
       <c r="C10" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="6">
         <v>46318</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -3100,8 +3069,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+    <row r="11" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -3110,7 +3079,7 @@
       <c r="C11" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="6">
         <v>46334</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -3120,8 +3089,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+    <row r="12" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -3130,7 +3099,7 @@
       <c r="C12" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="6">
         <v>46339</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -3140,8 +3109,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+    <row r="13" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -3150,7 +3119,7 @@
       <c r="C13" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="6">
         <v>46346</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -3160,8 +3129,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -3170,7 +3139,7 @@
       <c r="C14" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="6">
         <v>46371</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -3180,8 +3149,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -3190,7 +3159,7 @@
       <c r="C15" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="6">
         <v>46376</v>
       </c>
       <c r="E15" s="5" t="s">
@@ -3200,8 +3169,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+    <row r="16" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -3210,7 +3179,7 @@
       <c r="C16" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="6">
         <v>46392</v>
       </c>
       <c r="E16" s="5" t="s">
@@ -3220,8 +3189,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+    <row r="17" spans="1:6" ht="94.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -3230,7 +3199,7 @@
       <c r="C17" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="6">
         <v>46341</v>
       </c>
       <c r="E17" s="5" t="s">
@@ -3240,8 +3209,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+    <row r="18" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -3250,7 +3219,7 @@
       <c r="C18" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="6">
         <v>46310</v>
       </c>
       <c r="E18" s="5" t="s">
@@ -3260,8 +3229,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+    <row r="19" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -3270,7 +3239,7 @@
       <c r="C19" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="6">
         <v>46297</v>
       </c>
       <c r="E19" s="5" t="s">
@@ -3280,8 +3249,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+    <row r="20" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -3290,7 +3259,7 @@
       <c r="C20" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="6">
         <v>46295</v>
       </c>
       <c r="E20" s="5" t="s">
@@ -3300,8 +3269,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
+    <row r="21" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -3310,7 +3279,7 @@
       <c r="C21" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="6">
         <v>46301</v>
       </c>
       <c r="E21" s="5" t="s">
@@ -3320,8 +3289,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
+    <row r="22" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
@@ -3330,7 +3299,7 @@
       <c r="C22" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="6">
         <v>46311</v>
       </c>
       <c r="E22" s="5" t="s">
@@ -3340,8 +3309,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
+    <row r="23" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -3350,7 +3319,7 @@
       <c r="C23" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="6">
         <v>46322</v>
       </c>
       <c r="E23" s="5" t="s">
@@ -3360,8 +3329,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
+    <row r="24" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
@@ -3370,7 +3339,7 @@
       <c r="C24" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="6">
         <v>46392</v>
       </c>
       <c r="E24" s="5" t="s">
@@ -3380,8 +3349,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
+    <row r="25" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -3390,7 +3359,7 @@
       <c r="C25" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="6">
         <v>46470</v>
       </c>
       <c r="E25" s="5" t="s">
@@ -3400,8 +3369,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
+    <row r="26" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
@@ -3410,7 +3379,7 @@
       <c r="C26" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="6">
         <v>46487</v>
       </c>
       <c r="E26" s="5" t="s">
@@ -3420,92 +3389,84 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="C29" s="13" t="n">
-        <f aca="false">COUNTIF(F2:F26,"Done")</f>
+      <c r="C29" s="13">
+        <f>COUNTIF(F2:F26,"Done")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="C30" s="13" t="n">
-        <f aca="false">COUNTIF(F2:F26,"In progress")</f>
+      <c r="C30" s="13">
+        <f>COUNTIF(F2:F26,"In progress")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="13" t="n">
-        <f aca="false">COUNTIF(F2:F26,"Not started")</f>
+      <c r="C31" s="13">
+        <f>COUNTIF(F2:F26,"Not started")</f>
         <v>23</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="14" t="n">
-        <f aca="false">C29/COUNTA(F2:F26)</f>
+      <c r="C32" s="14">
+        <f>C29/COUNTA(F2:F26)</f>
         <v>0.04</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F26">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Not started"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F26" type="list">
+    <dataValidation type="list" sqref="F2:F26" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Not started,In progress,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>214</v>
       </c>
@@ -3525,8 +3486,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -3545,8 +3506,8 @@
         <v>224</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -3565,8 +3526,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -3585,8 +3546,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -3605,8 +3566,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -3625,8 +3586,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -3645,8 +3606,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+    <row r="8" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -3665,47 +3626,42 @@
         <v>251</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="11" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="11" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A14:F14"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/ADR_MPC_Project_Timeline.xlsx
+++ b/ADR_MPC_Project_Timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leonardo\Desktop\6 DOF-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAFA79E-AB04-4EEC-B39B-697884ED6B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1113E1-1A20-4458-A88E-B4EA8CC1E70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Timeline" sheetId="1" r:id="rId1"/>
@@ -891,9 +891,6 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -925,6 +922,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1246,1591 +1246,1591 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <v>46288</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>46289</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <f t="shared" ref="F2:F33" si="0">E2-D2</f>
         <v>1</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>46288</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>46292</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>46289</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>46291</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>46288</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>46297</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="H5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>46288</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>46293</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>46291</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>46298</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="5"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>46294</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>46298</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>46298</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>46301</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="5"/>
+      <c r="H9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>46301</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>46303</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="H10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="39.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>46301</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>46304</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="H11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>46303</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>46306</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="5" t="s">
+      <c r="H12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>46304</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>46308</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="5"/>
+      <c r="H13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>46307</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>46313</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="5"/>
+      <c r="H14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>46313</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="5">
         <v>46316</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="5" t="s">
+      <c r="H15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>46313</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="5">
         <v>46318</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="5"/>
+      <c r="H16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>46316</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="5">
         <v>46318</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="5" t="s">
+      <c r="H17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>46316</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="5">
         <v>46318</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="5"/>
+      <c r="H18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>46318</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="5">
         <v>46321</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="5"/>
+      <c r="H19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>46321</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>46323</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="5" t="s">
+      <c r="H20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>46323</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>46325</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="5" t="s">
+      <c r="H21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>46325</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="5">
         <v>46326</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="5"/>
+      <c r="H22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="3">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>46325</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="5">
         <v>46327</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="5" t="s">
+      <c r="H23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>46296</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="5">
         <v>46310</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="5"/>
+      <c r="H24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="3">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <v>46311</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="5">
         <v>46323</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="5"/>
+      <c r="H25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="7">
+      <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>46327</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <v>46327</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="9" t="s">
+      <c r="H26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="8" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <v>46327</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="5">
         <v>46447</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="5" t="s">
+      <c r="H27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="5">
         <v>46327</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="5">
         <v>46334</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="5"/>
+      <c r="H28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="3">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <v>46334</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="5">
         <v>46338</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="5"/>
+      <c r="H29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="3">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="5">
         <v>46336</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="5">
         <v>46339</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="5"/>
+      <c r="H30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="3">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="5">
         <v>46339</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="5">
         <v>46340</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="5"/>
+      <c r="H31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="3">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="5">
         <v>46340</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="5">
         <v>46346</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" s="5"/>
+      <c r="H32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="3">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="5">
         <v>46346</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="5">
         <v>46350</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="5"/>
+      <c r="H33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="3">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <v>46350</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="5">
         <v>46354</v>
       </c>
-      <c r="F34" s="3">
-        <f t="shared" ref="F34:F65" si="1">E34-D34</f>
+      <c r="F34" s="2">
+        <f t="shared" ref="F34:F53" si="1">E34-D34</f>
         <v>4</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="5"/>
+      <c r="H34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="3">
+      <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="5">
         <v>46354</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="5">
         <v>46357</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" s="5"/>
+      <c r="H35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="7">
+      <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="9">
         <v>46357</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="9">
         <v>46360</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" s="9" t="s">
+      <c r="H36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="8" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="3">
+      <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="5">
         <v>46360</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="5">
         <v>46371</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" s="5"/>
+      <c r="H37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="4"/>
     </row>
     <row r="38" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="3">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="5">
         <v>46366</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="5">
         <v>46376</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="2">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="5"/>
+      <c r="H38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="3">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="5">
         <v>46371</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="5">
         <v>46392</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="2">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" s="5"/>
+      <c r="H39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="3">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="5">
         <v>46392</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="5">
         <v>46402</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="2">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" s="5" t="s">
+      <c r="H40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="3">
+      <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="5">
         <v>46402</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="5">
         <v>46419</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="5" t="s">
+      <c r="H41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="3">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="5">
         <v>46419</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="5">
         <v>46430</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="2">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="5"/>
+      <c r="H42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="3">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="5">
         <v>46428</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="5">
         <v>46436</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="2">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" s="5" t="s">
+      <c r="H43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="7">
+      <c r="A44" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="9">
         <v>46436</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="9">
         <v>46443</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="6">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="H44" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="9" t="s">
+      <c r="H44" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="3">
+      <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="5">
         <v>46443</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="5">
         <v>46456</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="2">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="5"/>
+      <c r="H45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="3">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="5">
         <v>46456</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="5">
         <v>46470</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="2">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="5" t="s">
+      <c r="H46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="3">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="5">
         <v>46470</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="5">
         <v>46487</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="2">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="G47" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I47" s="5" t="s">
+      <c r="H47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" s="4" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="3">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="5">
         <v>46487</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="5">
         <v>46507</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="2">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I48" s="5" t="s">
+      <c r="H48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" s="4" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="3">
+      <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="5">
         <v>46507</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E49" s="5">
         <v>46522</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="2">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="G49" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" s="5" t="s">
+      <c r="H49" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" s="4" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="3">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="5">
         <v>46327</v>
       </c>
-      <c r="E50" s="6">
+      <c r="E50" s="5">
         <v>46341</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="2">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="G50" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="H50" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I50" s="5"/>
+      <c r="H50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="3">
+      <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="5">
         <v>46341</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51" s="5">
         <v>46348</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="2">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G51" s="5" t="s">
+      <c r="G51" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H51" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I51" s="5" t="s">
+      <c r="H51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="3">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="5">
         <v>46348</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="5">
         <v>46447</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="2">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
-      <c r="G52" s="5" t="s">
+      <c r="G52" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I52" s="5" t="s">
+      <c r="H52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="4" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="7">
+      <c r="A53" s="6">
         <v>52</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="9">
         <v>46461</v>
       </c>
-      <c r="E53" s="10">
+      <c r="E53" s="9">
         <v>46461</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H53" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" s="9" t="s">
+      <c r="H53" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="8" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="10" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C59" s="13">
+      <c r="C59" s="12">
         <f>COUNTIF(H2:H53,"Done")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C60" s="13">
+      <c r="C60" s="12">
         <f>COUNTIF(H2:H53,"In progress")</f>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="13">
+      <c r="C61" s="12">
         <f>COUNTIF(H2:H53,"Not started")</f>
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="14">
+      <c r="C62" s="13">
         <f>C59/COUNTA(H2:H53)</f>
-        <v>0.11538461538461539</v>
+        <v>0.15384615384615385</v>
       </c>
     </row>
   </sheetData>
@@ -2870,564 +2870,564 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <v>46289</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>46292</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46293</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="172.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="5">
+        <v>46298</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="5">
+        <v>46303</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D4" s="6">
-        <v>46293</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="172.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3">
+    <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="5">
+        <v>46308</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" s="5">
+        <v>46313</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="5">
+        <v>46316</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="5">
+        <v>46318</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="5">
+        <v>46334</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="5">
+        <v>46339</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="5">
+        <v>46346</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="5">
+        <v>46371</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46376</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46392</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="94.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" s="5">
+        <v>46341</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D18" s="5">
+        <v>46310</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19" s="5">
+        <v>46297</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46295</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D21" s="5">
+        <v>46301</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" s="5">
+        <v>46311</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" s="5">
+        <v>46322</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D24" s="5">
+        <v>46392</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D25" s="5">
+        <v>46470</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="5">
+        <v>46487</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C29" s="12">
+        <f>COUNTIF(F2:F26,"Done")</f>
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="6">
-        <v>46298</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D6" s="6">
-        <v>46303</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D7" s="6">
-        <v>46308</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D8" s="6">
-        <v>46313</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D9" s="6">
-        <v>46316</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D10" s="6">
-        <v>46318</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" s="6">
-        <v>46334</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D12" s="6">
-        <v>46339</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D13" s="6">
-        <v>46346</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D14" s="6">
-        <v>46371</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="3">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D15" s="6">
-        <v>46376</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="3">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D16" s="6">
-        <v>46392</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="94.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="3">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D17" s="6">
-        <v>46341</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="3">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D18" s="6">
-        <v>46310</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="3">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D19" s="6">
-        <v>46297</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="3">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D20" s="6">
-        <v>46295</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D21" s="6">
-        <v>46301</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="3">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" s="6">
-        <v>46311</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="3">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D23" s="6">
-        <v>46322</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="3">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D24" s="6">
-        <v>46392</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="3">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="D25" s="6">
-        <v>46470</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="3">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D26" s="6">
-        <v>46487</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="C29" s="13">
-        <f>COUNTIF(F2:F26,"Done")</f>
-        <v>1</v>
-      </c>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="12">
         <f>COUNTIF(F2:F26,"In progress")</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="12">
         <f>COUNTIF(F2:F26,"Not started")</f>
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="13">
         <f>C29/COUNTA(F2:F26)</f>
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -3467,194 +3467,194 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
     </row>
     <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/ADR_MPC_Project_Timeline.xlsx
+++ b/ADR_MPC_Project_Timeline.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leonardo\Desktop\6 DOF-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1113E1-1A20-4458-A88E-B4EA8CC1E70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E709B80C-84C2-416A-ABBD-9509CE46B51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Timeline" sheetId="1" r:id="rId1"/>
     <sheet name="Learning Plan" sheetId="2" r:id="rId2"/>
     <sheet name="Target Labs" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1236,7 +1237,7 @@
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="2" max="2" width="31.41796875" customWidth="1"/>
     <col min="3" max="3" width="52" customWidth="1"/>
     <col min="4" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
@@ -1560,7 +1561,7 @@
         <v>35</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>36</v>
@@ -1590,7 +1591,7 @@
         <v>38</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>39</v>
@@ -1620,7 +1621,7 @@
         <v>42</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -2803,7 +2804,7 @@
       </c>
       <c r="C59" s="12">
         <f>COUNTIF(H2:H53,"Done")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2821,7 +2822,7 @@
       </c>
       <c r="C61" s="12">
         <f>COUNTIF(H2:H53,"Not started")</f>
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2830,7 +2831,7 @@
       </c>
       <c r="C62" s="13">
         <f>C59/COUNTA(H2:H53)</f>
-        <v>0.15384615384615385</v>
+        <v>0.19230769230769232</v>
       </c>
     </row>
   </sheetData>
@@ -2986,7 +2987,7 @@
         <v>150</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3006,7 +3007,7 @@
         <v>153</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3246,7 +3247,7 @@
         <v>189</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3266,7 +3267,7 @@
         <v>192</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3286,7 +3287,7 @@
         <v>195</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3400,7 +3401,7 @@
       </c>
       <c r="C29" s="12">
         <f>COUNTIF(F2:F26,"Done")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3409,7 +3410,7 @@
       </c>
       <c r="C30" s="12">
         <f>COUNTIF(F2:F26,"In progress")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3418,7 +3419,7 @@
       </c>
       <c r="C31" s="12">
         <f>COUNTIF(F2:F26,"Not started")</f>
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3427,7 +3428,7 @@
       </c>
       <c r="C32" s="13">
         <f>C29/COUNTA(F2:F26)</f>
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
